--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -569,7 +569,7 @@
         <v>44036</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>43591</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44840</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45261</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45089</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>45132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>43557</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44008</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44021</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44806</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45174</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45261</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43504</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43699</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>43885</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44489</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44673</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44701</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>44812</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>44884</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44980</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45097</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45106</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45188</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45229</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45258</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45297</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45317</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>43348</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>43350</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>43353</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>43362</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>43378</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>43378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>43385</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>43385</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43412</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43412</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43412</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43412</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43412</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43412</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43423</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43423</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>43434</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>43438</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>43444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43445</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43447</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43448</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>43448</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>43448</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>43448</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>43452</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>43454</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>43455</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>43455</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>43461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>43467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>43467</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43467</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>43468</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>43468</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43474</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>43481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43481</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43483</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43483</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43489</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43500</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43500</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43500</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>43501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>43501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43502</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>43510</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43525</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43529</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43536</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43537</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43545</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43557</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43564</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43578</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>43585</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43585</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43598</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43608</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43608</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43608</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43614</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43618</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43618</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43618</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43618</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>43626</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>43626</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>43634</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>43635</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>43642</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>43643</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>43647</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>43648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>43689</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>43689</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>43689</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43699</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43700</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43700</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43705</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43713</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43714</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43717</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43718</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43725</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43725</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43725</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43746</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43748</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43748</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43754</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43761</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43767</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43773</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43774</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43788</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43790</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43790</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43793</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43798</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43801</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43812</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>43816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43816</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43822</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43833</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43837</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43840</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43847</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43850</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43857</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43879</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43887</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43899</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43922</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43922</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43928</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43930</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43930</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>43942</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43945</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43945</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43951</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43951</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43955</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43955</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43956</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43956</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43958</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43959</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43962</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43966</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43969</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43973</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43973</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43973</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43973</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>43976</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43976</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43976</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43977</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43978</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43979</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43979</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43980</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43983</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>43983</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>43984</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>43985</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>43986</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>43991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43991</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43992</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43994</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43994</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44004</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44004</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44004</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44005</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44007</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44007</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44007</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44007</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44011</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44011</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44012</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>44012</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44013</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44013</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44013</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44018</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44028</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44034</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44034</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44050</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44055</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44061</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44064</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44082</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44095</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44102</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44104</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44109</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44112</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44113</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44116</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44120</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>44124</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44127</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44127</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44130</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44132</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44138</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44139</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44139</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44139</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44147</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44152</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44154</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44167</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44172</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44172</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44174</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44188</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44190</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44190</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44190</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44190</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44203</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44208</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44208</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44218</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44218</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44221</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44223</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44231</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44231</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44235</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44236</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44237</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44237</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44242</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44249</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44249</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44258</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44258</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44263</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44263</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44263</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44284</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44284</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44287</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44301</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44305</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44305</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44305</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44309</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44312</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44313</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44319</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44320</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44329</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44330</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44337</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44342</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44348</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44348</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44349</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44349</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44349</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44350</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44355</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44355</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44357</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44357</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44357</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44362</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44362</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44364</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44379</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44382</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44386</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44396</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44403</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44417</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44421</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44421</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44432</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44434</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44435</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44439</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44439</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44440</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44441</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44442</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44442</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44448</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44452</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44454</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>44455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44456</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44460</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>44460</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44461</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44461</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44462</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44462</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44466</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44467</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44475</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44484</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44484</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44489</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44490</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44490</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44490</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44491</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44497</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44501</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44501</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44502</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44502</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44503</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44503</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44509</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44509</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44512</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44512</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44516</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44522</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44525</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44525</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44530</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44532</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44540</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44540</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44540</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44540</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44544</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44544</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44544</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44544</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44544</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44544</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44545</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44546</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44547</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44547</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>44551</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44552</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44552</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44552</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44552</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44558</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44560</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44566</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44571</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44573</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44574</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44575</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44575</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44579</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44581</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44586</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44586</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44589</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44594</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44595</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44596</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44596</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44596</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44599</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44601</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44601</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>44601</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44603</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44605</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44607</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44607</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44608</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44613</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44620</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44622</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44628</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44628</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44634</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44635</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44635</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44641</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44651</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44651</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44652</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44657</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44663</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44665</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44678</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44679</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44680</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44684</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44685</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44686</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44686</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44686</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44686</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44686</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>44690</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44690</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44690</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44691</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44692</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44692</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44692</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44699</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44699</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44699</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44701</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44705</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>44704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44705</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44705</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44706</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44706</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44711</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44713</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44714</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44713</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44720</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44720</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44720</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44722</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44722</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44722</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44725</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44728</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>44729</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44728</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44729</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44729</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44728</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44729</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44732</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44734</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44739</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44742</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44748</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44757</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44763</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44763</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44765</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44765</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44768</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44775</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44775</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44775</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44777</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44781</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>44782</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44783</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44783</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44785</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44788</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>44788</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44788</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>44788</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44789</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44789</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44789</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44792</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44792</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44797</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44797</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44798</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44799</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44804</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44806</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>44808</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44811</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44811</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44811</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44812</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44812</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44812</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44813</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44816</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44816</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44816</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44816</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44817</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44818</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44820</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>44823</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44823</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44823</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44823</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44824</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44825</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44825</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44825</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44826</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>44826</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44830</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44832</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44832</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44832</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44833</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44838</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44841</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44841</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44841</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44844</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44848</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44848</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44851</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44851</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44851</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44854</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44854</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44855</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44858</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44866</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44866</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44868</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44868</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44869</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44872</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44872</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44872</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>44873</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44873</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44873</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44874</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44874</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44874</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44874</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44874</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44876</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44879</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>44881</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44881</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>44881</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44886</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44886</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44886</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44886</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44887</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44888</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44888</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44888</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44888</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44888</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44893</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44893</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44894</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44894</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44895</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44896</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44896</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44897</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44900</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44900</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44900</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>44907</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>44915</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44915</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>44915</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44915</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44916</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44916</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44929</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>44929</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44929</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44930</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44930</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44937</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44937</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44938</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>44938</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>44939</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>44939</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44942</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44943</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>44943</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44945</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44945</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>44949</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44952</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44952</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>44952</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44952</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>44952</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44952</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>44953</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44958</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44959</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44959</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44960</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44960</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>44960</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44964</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44964</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44964</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44965</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44965</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44967</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44968</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44968</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44970</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44973</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>44979</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44980</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44980</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44980</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44980</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44980</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>44980</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44985</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44985</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44985</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44987</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44993</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44993</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44994</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44998</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44999</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>44999</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44999</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44999</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45001</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45016</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45019</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45019</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45019</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45020</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45020</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45020</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45027</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45029</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45029</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45034</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45041</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45041</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45042</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45043</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45044</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45044</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45044</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45044</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45045</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45055</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45056</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45058</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45061</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45062</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45062</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45062</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45063</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45063</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45063</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45068</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45069</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45069</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45071</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45072</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45072</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45075</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45075</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45075</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45075</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45078</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45079</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45079</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45079</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45079</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>45086</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45086</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45089</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45089</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45090</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45090</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45099</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45099</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45103</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45103</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45103</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45103</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45104</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45105</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45106</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45106</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45106</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45120</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45120</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45121</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45121</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45122</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45124</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45125</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45131</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45132</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45139</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45140</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45142</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45142</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45142</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45142</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45142</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45142</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>45142</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45146</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45149</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45149</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45152</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45152</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45154</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45154</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45155</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45161</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45161</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45162</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45163</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45163</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45163</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45163</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45163</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45163</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45166</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45166</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45167</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45167</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45168</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45168</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45169</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45169</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45169</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45169</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>45169</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45169</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45170</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45170</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45170</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45170</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45173</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45173</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45174</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45174</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45174</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45174</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45175</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45175</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45175</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45175</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45175</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45176</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45176</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45176</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45176</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45177</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45182</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45182</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45183</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45183</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45184</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45183</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45187</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45187</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45188</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45188</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45188</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45188</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45188</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45189</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45189</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45191</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45195</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45195</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45196</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45197</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>45197</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45202</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45202</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45204</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45204</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45208</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45208</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45215</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45216</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45216</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45216</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>45216</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59860,7 +59860,7 @@
         <v>45216</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45216</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45216</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45216</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45216</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45216</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45217</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45218</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45218</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45218</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>45219</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45219</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45219</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45219</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45219</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45222</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45222</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45222</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45223</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45223</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45223</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>45231</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>45231</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45231</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45231</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45231</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45232</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45232</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45232</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45233</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45232</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45233</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45236</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45236</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45236</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45236</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45236</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45236</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45236</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45236</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45238</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45239</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45239</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45240</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45240</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>45243</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45245</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45246</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45246</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45246</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45246</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63011,7 +63011,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45252</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45253</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45257</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45258</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>45259</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45260</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63715,7 +63715,7 @@
         <v>45260</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45261</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45264</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45266</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45267</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45267</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45267</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45268</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         <v>45268</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45269</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45271</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45271</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45271</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45271</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45272</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45272</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45273</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45275</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45287</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45288</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45288</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45289</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45295</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45296</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>45296</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -65242,7 +65242,7 @@
         <v>45296</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45297</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>45297</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45299</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45299</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45300</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45301</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45303</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45303</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45303</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>45306</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45306</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45306</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45309</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45309</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -66115,14 +66115,14 @@
     <row r="1094" ht="15" customHeight="1">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>A 2566-2024</t>
+          <t>A 2569-2024</t>
         </is>
       </c>
       <c r="B1094" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         </is>
       </c>
       <c r="G1094" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -66172,14 +66172,14 @@
     <row r="1095" ht="15" customHeight="1">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>A 2569-2024</t>
+          <t>A 2573-2024</t>
         </is>
       </c>
       <c r="B1095" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -66192,7 +66192,7 @@
         </is>
       </c>
       <c r="G1095" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -66229,14 +66229,14 @@
     <row r="1096" ht="15" customHeight="1">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>A 2573-2024</t>
+          <t>A 2566-2024</t>
         </is>
       </c>
       <c r="B1096" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -66249,7 +66249,7 @@
         </is>
       </c>
       <c r="G1096" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -66293,7 +66293,7 @@
         <v>45320</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45324</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>45327</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66474,7 +66474,7 @@
         <v>45331</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>45336</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45336</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1102"/>
+  <dimension ref="A1:Z1103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44036</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>43591</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44840</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45261</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45089</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>45132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>43557</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44008</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44021</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44806</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45174</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45261</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43504</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43699</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>43885</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44489</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44673</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44701</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>44812</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>44884</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44980</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45097</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45106</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45188</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45229</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45258</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45297</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45317</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>43348</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>43350</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>43353</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>43362</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>43378</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>43378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>43385</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>43385</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43412</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43412</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43412</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43412</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43412</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43412</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43423</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43423</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>43434</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>43438</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>43444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43445</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43447</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43448</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>43448</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>43448</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>43448</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>43452</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>43454</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>43455</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>43455</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>43461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>43467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>43467</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43467</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>43468</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>43468</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43474</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>43481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43481</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43483</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43483</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43489</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43500</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43500</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43500</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>43501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>43501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43502</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>43510</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43525</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43529</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43536</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43537</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43545</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43557</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43564</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43578</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>43585</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43585</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43598</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43608</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43608</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43608</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43614</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43618</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43618</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43618</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43618</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>43626</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>43626</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>43634</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>43635</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>43642</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>43643</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>43647</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>43648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>43689</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>43689</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>43689</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43699</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43700</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43700</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43705</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43713</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43714</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43717</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43718</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43725</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43725</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43725</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43746</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43748</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43748</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43754</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43761</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43767</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43773</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43774</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43788</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43790</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43790</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43793</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43798</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43801</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43812</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>43816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43816</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43822</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43833</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43837</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43840</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43847</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43850</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43857</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43879</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43887</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43899</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43922</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43922</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43928</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43930</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43930</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>43942</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43945</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43945</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43951</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43951</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43955</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43955</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43956</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43956</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43958</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43959</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43962</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43966</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43969</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43973</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43973</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43973</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43973</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>43976</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43976</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43976</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43977</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43978</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43979</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43979</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43980</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43983</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>43983</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>43984</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>43985</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>43986</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>43991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43991</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43992</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43994</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43994</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44004</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44004</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44004</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44005</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44007</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44007</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44007</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44007</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44011</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44011</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44012</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>44012</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44013</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44013</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44013</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44018</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44028</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44034</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44034</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44050</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44055</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44061</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44064</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44082</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44095</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44102</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44104</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44109</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44112</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44113</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44116</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44120</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>44124</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44127</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44127</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44130</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44132</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44138</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44139</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44139</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44139</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44147</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44152</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44154</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44167</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44172</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44172</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44174</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44188</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44190</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44190</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44190</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44190</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44203</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44208</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44208</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44218</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44218</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44221</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44223</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44231</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44231</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44235</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44236</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44237</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44237</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44242</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44249</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44249</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44258</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44258</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44263</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44263</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44263</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44284</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44284</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44287</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44301</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44305</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44305</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44305</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44309</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44312</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44313</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44319</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44320</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44329</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44330</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44337</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44342</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44348</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44348</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44349</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44349</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44349</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44350</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44355</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44355</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44357</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44357</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44357</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44362</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44362</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44364</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44379</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44382</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44386</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44396</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44403</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44417</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44421</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44421</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44432</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44434</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44435</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44439</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44439</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44440</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44441</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44442</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44442</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44448</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44452</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44454</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>44455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44456</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44460</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>44460</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44461</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44461</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44462</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44462</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44466</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44467</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44475</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44484</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44484</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44489</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44490</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44490</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44490</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44491</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44497</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44501</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44501</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44502</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44502</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44503</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44503</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44509</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44509</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44512</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44512</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44516</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44522</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44525</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44525</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44530</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44532</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44540</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44540</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44540</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44540</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44544</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44544</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44544</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44544</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44544</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44544</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44545</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44546</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44547</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44547</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>44551</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44552</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44552</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44552</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44552</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44558</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44560</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44566</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44571</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44573</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44574</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44575</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44575</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44579</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44581</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44586</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44586</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44589</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44594</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44595</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44596</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44596</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44596</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44599</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44601</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44601</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>44601</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44603</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44605</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44607</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44607</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44608</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44613</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44620</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44622</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44628</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44628</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44634</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44635</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44635</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44641</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44651</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44651</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44652</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44657</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44663</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44665</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44678</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44679</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44680</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44684</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44685</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44686</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44686</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44686</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44686</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44686</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>44690</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44690</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44690</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44691</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44692</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44692</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44692</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44699</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44699</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44699</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44701</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44705</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>44704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44705</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44705</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44706</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44706</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44711</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44713</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44714</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44713</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44720</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44720</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44720</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44722</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44722</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44722</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44725</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44728</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>44729</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44728</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44729</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44729</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44728</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44729</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44732</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44734</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44739</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44742</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44748</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44757</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44763</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44763</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44765</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44765</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44768</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44775</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44775</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44775</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44777</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44781</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>44782</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44783</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44783</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44785</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44788</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>44788</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44788</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>44788</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44789</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44789</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44789</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44792</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44792</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44797</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44797</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44798</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44799</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44804</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44806</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>44808</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44811</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44811</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44811</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44812</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44812</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44812</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44813</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44816</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44816</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44816</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44816</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44817</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44818</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44820</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>44823</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44823</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44823</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44823</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44824</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44825</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44825</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44825</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44826</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>44826</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44830</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44832</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44832</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44832</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44833</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44838</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44841</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44841</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44841</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44844</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44848</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44848</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44851</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44851</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44851</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44854</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44854</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44855</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44858</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44866</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44866</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44868</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44868</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44869</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44872</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44872</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44872</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>44873</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44873</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44873</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44874</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44874</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44874</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44874</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44874</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44876</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44879</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>44881</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44881</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>44881</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44886</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44886</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44886</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44886</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44887</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44888</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44888</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44888</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44888</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44888</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44893</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44893</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44894</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44894</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44895</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44896</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44896</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44897</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44900</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44900</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44900</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>44907</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>44915</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44915</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>44915</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44915</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44916</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44916</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44929</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>44929</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44929</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44930</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44930</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44937</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44937</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44938</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>44938</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>44939</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>44939</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44942</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44943</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>44943</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44945</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44945</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>44949</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44952</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44952</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>44952</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44952</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>44952</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44952</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>44953</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44958</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44959</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44959</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44960</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44960</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>44960</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44964</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44964</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44964</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44965</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44965</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44967</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44968</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44968</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44970</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44973</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>44979</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44980</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44980</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44980</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44980</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44980</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>44980</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44985</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44985</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44985</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44987</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44993</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44993</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44994</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44998</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44999</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>44999</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44999</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44999</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45001</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45016</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45019</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45019</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45019</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45020</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45020</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45020</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45027</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45029</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45029</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45034</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45041</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45041</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45042</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45043</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45044</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45044</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45044</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45044</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45045</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45055</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45056</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45058</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45061</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45062</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45062</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45062</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45063</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45063</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45063</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45068</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45069</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45069</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45071</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45072</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45072</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45075</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45075</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45075</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45075</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45078</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45079</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45079</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45079</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45079</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>45086</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45086</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45089</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45089</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45090</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45090</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45099</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45099</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45103</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45103</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45103</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45103</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45104</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45105</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45106</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45106</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45106</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45120</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45120</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45121</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45121</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45122</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45124</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45125</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45131</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45132</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45139</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45140</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45142</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45142</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45142</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45142</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45142</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45142</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>45142</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45146</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45149</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45149</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45152</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45152</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45154</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45154</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45155</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45161</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45161</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45162</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45163</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45163</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45163</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45163</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45163</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45163</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45166</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45166</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45167</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45167</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45168</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45168</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45169</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45169</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45169</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45169</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>45169</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45169</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45170</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45170</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45170</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45170</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45173</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45173</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45174</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45174</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45174</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45174</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45175</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45175</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45175</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45175</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45175</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45176</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45176</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45176</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45176</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45177</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45182</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45182</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45183</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45183</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45184</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45183</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45187</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45187</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45188</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45188</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45188</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45188</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45188</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45189</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45189</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45191</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45195</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45195</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45196</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45197</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>45197</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45202</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45202</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45204</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45204</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45208</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45208</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45215</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45216</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45216</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45216</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>45216</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59860,7 +59860,7 @@
         <v>45216</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45216</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45216</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45216</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45216</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45216</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45217</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45218</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45218</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45218</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>45219</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45219</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45219</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45219</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45219</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45222</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45222</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45222</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45223</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45223</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45223</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>45231</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>45231</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45231</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45231</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45231</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45232</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45232</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45232</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45233</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45232</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45233</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45236</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45236</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45236</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45236</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45236</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45236</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45236</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45236</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45238</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45239</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45239</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45240</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45240</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>45243</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45245</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45246</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45246</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45246</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45246</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63011,7 +63011,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45252</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45253</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45257</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45258</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>45259</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45260</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63715,7 +63715,7 @@
         <v>45260</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45261</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45264</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45266</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45267</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45267</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45267</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45268</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         <v>45268</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45269</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45271</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45271</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45271</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45271</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45272</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45272</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45273</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45275</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45287</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45288</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45288</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45289</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45295</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45296</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>45296</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -65242,7 +65242,7 @@
         <v>45296</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45297</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>45297</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45299</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45299</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45300</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45301</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45303</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45303</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45303</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>45306</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45306</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45306</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45309</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45309</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>45313</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45313</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45313</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45320</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45324</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>45327</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66474,7 +66474,7 @@
         <v>45331</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>45336</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
       </c>
       <c r="R1101" s="2" t="inlineStr"/>
     </row>
-    <row r="1102">
+    <row r="1102" ht="15" customHeight="1">
       <c r="A1102" t="inlineStr">
         <is>
           <t>A 5999-2024</t>
@@ -66588,7 +66588,7 @@
         <v>45336</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -66634,6 +66634,63 @@
         <v>0</v>
       </c>
       <c r="R1102" s="2" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>A 6467-2024</t>
+        </is>
+      </c>
+      <c r="B1103" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C1103" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>NORDANSTIG</t>
+        </is>
+      </c>
+      <c r="G1103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -569,7 +569,7 @@
         <v>44036</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>43591</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44840</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45261</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45089</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>45132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>43557</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44008</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44021</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44806</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45174</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45261</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43504</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43699</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>43885</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44489</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44673</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44701</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>44812</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>44884</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44980</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45097</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45106</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45188</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45229</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45258</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45297</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45317</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>43348</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>43350</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>43353</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>43362</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>43378</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>43378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>43385</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>43385</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43412</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43412</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43412</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43412</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43412</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43412</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43423</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43423</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>43434</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>43438</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>43444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43445</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43447</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43448</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>43448</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>43448</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>43448</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>43452</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>43454</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>43455</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>43455</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>43461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>43467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>43467</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43467</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>43468</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>43468</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43474</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>43481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43481</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43483</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43483</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43489</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43500</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43500</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43500</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>43501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>43501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43502</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>43510</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43525</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43529</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43536</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43537</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43545</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43557</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43564</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43578</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>43585</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43585</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43598</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43608</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43608</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43608</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43614</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43618</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43618</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43618</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43618</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>43626</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>43626</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>43634</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>43635</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>43642</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>43643</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>43647</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>43648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>43689</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>43689</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>43689</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43699</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43700</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43700</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43705</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43713</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43714</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43717</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43718</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43725</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43725</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43725</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43746</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43748</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43748</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43754</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43761</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43767</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43773</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43774</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43788</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43790</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43790</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43793</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43798</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43801</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43812</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>43816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43816</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43822</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43833</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43837</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43840</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43847</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43850</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43857</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43879</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43887</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43899</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43922</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43922</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43928</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43930</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43930</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>43942</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43945</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43945</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43951</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43951</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43955</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43955</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43956</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43956</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43958</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43959</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43962</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43966</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43969</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43973</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43973</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43973</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43973</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>43976</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43976</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43976</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43977</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43978</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43979</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43979</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43980</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43983</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>43983</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>43984</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>43985</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>43986</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>43991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43991</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43992</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43994</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43994</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44004</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44004</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44004</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44005</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44007</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44007</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44007</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44007</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44011</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44011</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44012</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>44012</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44013</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44013</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44013</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44018</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44028</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44034</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44034</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44050</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44055</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44061</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44064</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44082</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44095</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44102</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44104</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44109</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44112</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44113</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44116</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44120</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>44124</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44127</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44127</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44130</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44132</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44138</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44139</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44139</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44139</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44147</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44152</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44154</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44167</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44172</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44172</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44174</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44188</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44190</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44190</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44190</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44190</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44203</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44208</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44208</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44218</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44218</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44221</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44223</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44231</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44231</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44235</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44236</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44237</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44237</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44242</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44249</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44249</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44258</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44258</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44263</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44263</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44263</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44284</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44284</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44287</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44301</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44305</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44305</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44305</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44309</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44312</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44313</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44319</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44320</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44329</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44330</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44337</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44342</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44348</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44348</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44349</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44349</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44349</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44350</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44355</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44355</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44357</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44357</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44357</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44362</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44362</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44364</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44379</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44382</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44386</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44396</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44403</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44417</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44421</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44421</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44432</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44434</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44435</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44439</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44439</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44440</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44441</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44442</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44442</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44448</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44452</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44454</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>44455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44456</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44460</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>44460</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44461</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44461</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44462</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44462</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44466</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44467</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44475</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44484</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44484</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44489</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44490</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44490</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44490</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44491</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44497</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44501</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44501</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44502</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44502</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44503</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44503</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44509</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44509</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44512</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44512</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44516</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44522</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44525</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44525</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44530</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44532</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44540</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44540</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44540</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44540</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44544</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44544</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44544</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44544</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44544</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44544</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44545</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44546</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44547</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44547</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>44551</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44552</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44552</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44552</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44552</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44558</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44560</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44566</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44571</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44573</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44574</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44575</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44575</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44579</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44581</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44586</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44586</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44589</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44594</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44595</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44596</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44596</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44596</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44599</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44601</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44601</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>44601</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44603</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44605</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44607</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44607</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44608</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44613</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44620</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44622</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44628</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44628</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44634</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44635</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44635</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44641</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44651</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44651</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44652</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44657</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44663</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44665</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44678</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44679</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44680</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44684</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44685</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44686</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44686</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44686</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44686</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44686</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>44690</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44690</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44690</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44691</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44692</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44692</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44692</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44699</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44699</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44699</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44701</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44705</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>44704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44705</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44705</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44706</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44706</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44711</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44713</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44714</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44713</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44720</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44720</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44720</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44722</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44722</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44722</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44725</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44728</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>44729</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44728</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44729</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44729</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44728</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44729</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44732</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44734</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44739</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44742</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44748</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44757</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44763</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44763</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44765</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44765</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44768</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44775</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44775</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44775</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44777</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44781</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>44782</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44783</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44783</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44785</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44788</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>44788</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44788</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>44788</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44789</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44789</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44789</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44792</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44792</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44797</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44797</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44798</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44799</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44804</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44806</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>44808</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44811</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44811</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44811</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44812</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44812</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44812</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44813</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44816</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44816</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44816</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44816</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44817</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44818</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44820</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>44823</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44823</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44823</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44823</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44824</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44825</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44825</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44825</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44826</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>44826</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44830</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44832</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44832</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44832</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44833</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44838</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44841</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44841</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44841</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44844</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44848</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44848</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44851</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44851</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44851</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44854</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44854</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44855</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44858</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44866</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44866</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44868</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44868</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44869</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44872</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44872</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44872</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>44873</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44873</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44873</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44874</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44874</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44874</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44874</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44874</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44876</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44879</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>44881</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44881</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>44881</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44886</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44886</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44886</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44886</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44887</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44888</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44888</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44888</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44888</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44888</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44893</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44893</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44894</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44894</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44895</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44896</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44896</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44897</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44900</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44900</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44900</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>44907</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>44915</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44915</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>44915</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44915</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44916</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44916</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44929</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>44929</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44929</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44930</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44930</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44937</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44937</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44938</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>44938</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>44939</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>44939</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44942</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44943</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>44943</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44945</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44945</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>44949</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44952</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44952</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>44952</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44952</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>44952</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44952</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>44953</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44958</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44959</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44959</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44960</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44960</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>44960</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44964</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44964</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44964</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44965</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44965</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44967</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44968</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44968</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44970</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44973</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>44979</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44980</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44980</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44980</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44980</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44980</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>44980</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44985</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44985</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44985</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44987</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44993</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44993</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44994</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44998</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44999</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>44999</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44999</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44999</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45001</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45016</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45019</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45019</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45019</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45020</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45020</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45020</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45027</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45029</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45029</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45034</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45041</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45041</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45042</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45043</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45044</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45044</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45044</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45044</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45045</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45055</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45056</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45058</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45061</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45062</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45062</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45062</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45063</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45063</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45063</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45068</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45069</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45069</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45071</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45072</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45072</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45075</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45075</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45075</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45075</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45078</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45079</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45079</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45079</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45079</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>45086</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45086</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45089</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45089</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45090</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45090</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45099</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45099</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45103</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45103</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45103</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45103</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45104</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45105</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45106</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45106</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45106</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45120</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45120</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45121</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45121</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45122</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45124</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45125</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45131</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45132</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45139</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45140</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45142</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45142</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45142</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45142</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45142</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45142</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>45142</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45146</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45149</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45149</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45152</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45152</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45154</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45154</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45155</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45161</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45161</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45162</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45163</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45163</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45163</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45163</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45163</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45163</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45166</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45166</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45167</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45167</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45168</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45168</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45169</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45169</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45169</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45169</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>45169</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45169</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45170</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45170</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45170</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45170</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45173</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45173</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45174</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45174</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45174</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45174</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45175</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45175</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45175</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45175</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45175</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45176</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45176</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45176</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45176</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45177</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45182</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45182</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45183</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45183</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45184</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45183</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45187</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45187</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45188</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45188</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45188</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45188</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45188</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45189</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45189</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45191</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45195</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45195</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45196</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45197</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>45197</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45202</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45202</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45204</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45204</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45208</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45208</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45215</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45216</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45216</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45216</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>45216</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59860,7 +59860,7 @@
         <v>45216</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45216</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45216</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45216</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45216</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45216</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45217</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45218</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45218</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45218</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>45219</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45219</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45219</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45219</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45219</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45222</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45222</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45222</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45223</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45223</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45223</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>45231</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>45231</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45231</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45231</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45231</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45232</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45232</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45232</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45233</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45232</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45233</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45236</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45236</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45236</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45236</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45236</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45236</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45236</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45236</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45238</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45239</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45239</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45240</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45240</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>45243</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45245</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45246</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45246</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45246</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45246</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63011,7 +63011,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45252</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45253</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45257</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45258</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>45259</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45260</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63715,7 +63715,7 @@
         <v>45260</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45261</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45264</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45266</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45267</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45267</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45267</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45268</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         <v>45268</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45269</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45271</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45271</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45271</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45271</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45272</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45272</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45273</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45275</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45287</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45288</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45288</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45289</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45295</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45296</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>45296</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -65242,7 +65242,7 @@
         <v>45296</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45297</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>45297</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45299</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45299</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45300</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45301</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45303</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45303</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45303</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>45306</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45306</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45306</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45309</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45309</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>45313</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45313</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45313</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45320</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45324</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>45327</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66474,7 +66474,7 @@
         <v>45331</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>45336</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45336</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>45338</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -569,7 +569,7 @@
         <v>44036</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>43591</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44840</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45261</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45089</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>45132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>43557</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44008</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44021</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44806</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45174</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45261</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43504</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43699</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>43885</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44489</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44673</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44701</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>44812</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>44884</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44980</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45097</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45106</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45188</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45229</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45258</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45297</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45317</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>43348</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>43350</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>43353</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>43362</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>43378</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>43378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>43385</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>43385</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43412</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43412</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43412</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43412</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43412</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43412</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43423</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43423</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>43434</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>43438</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>43444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43445</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43447</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43448</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>43448</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>43448</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>43448</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>43452</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>43454</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>43455</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>43455</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>43461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>43467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>43467</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43467</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>43468</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>43468</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43474</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>43481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43481</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43483</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43483</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43489</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43500</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43500</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43500</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>43501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>43501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43502</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>43510</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43525</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43529</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43536</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43537</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43545</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43557</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43564</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43578</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>43585</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43585</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43598</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43608</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43608</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43608</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43614</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43618</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43618</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43618</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43618</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>43626</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>43626</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>43634</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>43635</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>43642</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>43643</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>43647</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>43648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>43689</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>43689</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>43689</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43699</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43700</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43700</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43705</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43713</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43714</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43717</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43718</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43725</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43725</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43725</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43746</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43748</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43748</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43754</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43761</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43767</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43773</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43774</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43788</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43790</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43790</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43793</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43798</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43801</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43812</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>43816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43816</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43822</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43833</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43837</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43840</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43847</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43850</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43857</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43879</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43887</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43899</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43922</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43922</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43928</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43930</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43930</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>43942</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43945</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43945</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43951</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43951</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43955</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43955</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43956</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43956</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43958</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43959</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43962</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43966</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43969</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43973</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43973</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43973</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43973</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>43976</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43976</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43976</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43977</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43978</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43979</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43979</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43980</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43983</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>43983</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>43984</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>43985</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>43986</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>43991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43991</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43992</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43994</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43994</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44004</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44004</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44004</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44005</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44007</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44007</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44007</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44007</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44011</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44011</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44012</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>44012</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44013</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44013</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44013</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44018</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44028</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44034</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44034</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44050</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44055</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44061</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44064</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44082</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44095</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44102</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44104</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44109</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44112</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44113</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44116</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44120</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>44124</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44127</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44127</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44130</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44132</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44138</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44139</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44139</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44139</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44147</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44152</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44154</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44167</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44172</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44172</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44174</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44188</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44190</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44190</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44190</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44190</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44203</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44208</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44208</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44218</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44218</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44221</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44223</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44231</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44231</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44235</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44236</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44237</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44237</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44242</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44249</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44249</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44258</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44258</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44263</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44263</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44263</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44284</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44284</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44287</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44301</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44305</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44305</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44305</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44309</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44312</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44313</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44319</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44320</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44329</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44330</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44337</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44342</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44348</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44348</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44349</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44349</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44349</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44350</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44355</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44355</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44357</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44357</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44357</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44362</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44362</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44364</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44379</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44382</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44386</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44396</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44403</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44417</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44421</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44421</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44432</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44434</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44435</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44439</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44439</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44440</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44441</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44442</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44442</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44448</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44452</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44454</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>44455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44456</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44460</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>44460</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44461</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44461</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44462</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44462</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44466</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44467</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44475</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44484</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44484</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44489</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44490</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44490</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44490</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44491</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44497</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44501</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44501</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44502</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44502</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44503</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44503</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44509</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44509</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44512</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44512</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44516</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44522</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44525</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44525</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44530</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44532</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44540</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44540</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44540</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44540</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44544</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44544</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44544</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44544</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44544</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44544</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44545</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44546</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44547</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44547</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>44551</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44552</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44552</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44552</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44552</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44558</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44560</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44566</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44571</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44573</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44574</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44575</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44575</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44579</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44581</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44586</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44586</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44589</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44594</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44595</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44596</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44596</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44596</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44599</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44601</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44601</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>44601</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44603</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44605</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44607</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44607</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44608</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44613</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44620</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44622</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44628</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44628</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44634</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44635</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44635</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44641</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44651</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44651</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44652</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44657</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44663</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44665</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44678</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44679</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44680</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44684</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44685</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44686</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44686</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44686</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44686</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44686</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>44690</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44690</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44690</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44691</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44692</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44692</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44692</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44699</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44699</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44699</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44701</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44705</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>44704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44705</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44705</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44706</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44706</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44711</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44713</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44714</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44713</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44720</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44720</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44720</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44722</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44722</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44722</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44725</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44728</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>44729</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44728</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44729</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44729</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44728</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44729</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44732</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44734</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44739</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44742</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44748</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44757</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44763</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44763</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44765</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44765</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44768</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44775</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44775</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44775</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44777</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44781</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>44782</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44783</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44783</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44785</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44788</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>44788</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44788</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>44788</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44789</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44789</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44789</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44792</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44792</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44797</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44797</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44798</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44799</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44804</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44806</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>44808</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44811</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44811</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44811</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44812</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44812</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44812</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44813</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44816</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44816</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44816</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44816</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44817</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44818</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44820</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>44823</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44823</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44823</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44823</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44824</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44825</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44825</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44825</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44826</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>44826</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44830</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44832</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44832</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44832</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44833</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44838</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44841</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44841</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44841</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44844</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44848</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44848</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44851</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44851</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44851</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44854</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44854</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44855</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44858</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44866</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44866</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44868</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44868</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44869</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44872</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44872</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44872</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>44873</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44873</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44873</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44874</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44874</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44874</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44874</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44874</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44876</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44879</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>44881</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44881</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>44881</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44886</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44886</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44886</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44886</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44887</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44888</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44888</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44888</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44888</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44888</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44893</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44893</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44894</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44894</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44895</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44896</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44896</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44897</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44900</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44900</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44900</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>44907</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>44915</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44915</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>44915</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44915</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44916</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44916</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44929</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>44929</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44929</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44930</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44930</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44937</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44937</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44938</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>44938</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>44939</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>44939</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44942</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44943</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>44943</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44945</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44945</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>44949</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44952</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44952</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>44952</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44952</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>44952</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44952</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>44953</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44958</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44959</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44959</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44960</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44960</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>44960</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44964</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44964</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44964</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44965</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44965</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44967</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44968</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44968</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44970</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44973</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>44979</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44980</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44980</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44980</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44980</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44980</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>44980</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44985</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44985</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44985</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44987</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44993</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44993</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44994</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44998</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44999</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>44999</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44999</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44999</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45001</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45016</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45019</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45019</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45019</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45020</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45020</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45020</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45027</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45029</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45029</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45034</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45041</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45041</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45042</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45043</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45044</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45044</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45044</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45044</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45045</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45055</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45056</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45058</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45061</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45062</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45062</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45062</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45063</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45063</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45063</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45068</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45069</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45069</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45071</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45072</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45072</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45075</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45075</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45075</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45075</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45078</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45079</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45079</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45079</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45079</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>45086</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45086</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45089</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45089</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45090</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45090</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45099</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45099</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45103</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45103</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45103</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45103</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45104</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45105</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45106</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45106</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45106</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45120</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45120</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45121</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45121</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45122</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45124</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45125</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45131</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45132</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45139</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45140</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45142</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45142</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45142</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45142</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45142</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45142</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>45142</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45146</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45149</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45149</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45152</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45152</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45154</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45154</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45155</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45161</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45161</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45162</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45163</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45163</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45163</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45163</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45163</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45163</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45166</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45166</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45167</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45167</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45168</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45168</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45169</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45169</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45169</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45169</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>45169</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45169</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45170</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45170</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45170</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45170</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45173</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45173</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45174</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45174</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45174</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45174</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45175</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45175</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45175</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45175</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45175</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45176</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45176</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45176</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45176</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45177</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45182</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45182</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45183</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45183</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45184</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45183</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45187</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45187</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45188</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45188</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45188</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45188</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45188</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45189</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45189</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45191</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45195</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45195</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45196</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45197</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>45197</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45202</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45202</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45204</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45204</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45208</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45208</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45215</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45216</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45216</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45216</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>45216</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59860,7 +59860,7 @@
         <v>45216</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45216</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45216</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45216</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45216</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45216</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45217</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45218</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45218</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45218</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>45219</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45219</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45219</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45219</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45219</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45222</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45222</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45222</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45223</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45223</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45223</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>45231</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>45231</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45231</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45231</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45231</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45232</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45232</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45232</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45233</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45232</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45233</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45236</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45236</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45236</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45236</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45236</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45236</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45236</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45236</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45238</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45239</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45239</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45240</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45240</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>45243</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45245</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45246</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45246</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45246</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45246</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63011,7 +63011,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45252</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45253</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45257</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45258</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>45259</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45260</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63715,7 +63715,7 @@
         <v>45260</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45261</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45264</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45266</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45267</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45267</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45267</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45268</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         <v>45268</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45269</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45271</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45271</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45271</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45271</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45272</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45272</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45273</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45275</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45287</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45288</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45288</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45289</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45295</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45296</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>45296</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -65242,7 +65242,7 @@
         <v>45296</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45297</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>45297</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45299</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45299</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45300</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45301</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45303</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45303</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45303</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>45306</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45306</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45306</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45309</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45309</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>45313</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45313</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45313</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45320</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45324</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>45327</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66474,7 +66474,7 @@
         <v>45331</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>45336</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45336</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>45338</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -66695,14 +66695,14 @@
     <row r="1104" ht="15" customHeight="1">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>A 6923-2024</t>
+          <t>A 7080-2024</t>
         </is>
       </c>
       <c r="B1104" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -66714,13 +66714,8 @@
           <t>NORDANSTIG</t>
         </is>
       </c>
-      <c r="F1104" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="G1104" t="n">
-        <v>1.1</v>
+        <v>20.9</v>
       </c>
       <c r="H1104" t="n">
         <v>0</v>
@@ -66757,14 +66752,14 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>A 7080-2024</t>
+          <t>A 6923-2024</t>
         </is>
       </c>
       <c r="B1105" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -66776,8 +66771,13 @@
           <t>NORDANSTIG</t>
         </is>
       </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="G1105" t="n">
-        <v>20.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1105" t="n">
         <v>0</v>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -569,7 +569,7 @@
         <v>44036</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>43591</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44840</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45261</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45089</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>45132</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>43557</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44008</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44021</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44806</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45174</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45261</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43504</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43699</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>43885</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44489</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44673</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44701</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>44812</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>44884</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44980</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45097</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45106</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45188</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45229</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45258</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45297</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45317</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>43348</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>43350</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>43353</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>43362</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>43378</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>43378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>43385</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>43385</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43412</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43412</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43412</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43412</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43412</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43412</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43423</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43423</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>43434</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>43438</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>43440</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>43440</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43441</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>43444</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43445</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43447</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43448</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>43448</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>43448</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>43448</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>43452</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>43454</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>43455</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>43455</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>43461</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>43467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>43467</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43467</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>43468</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>43468</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>43468</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43474</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>43481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43481</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43483</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43483</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43489</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43500</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43500</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43500</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>43501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>43501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43502</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>43510</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43525</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43529</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43536</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43537</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43545</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43557</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43564</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43578</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>43585</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43585</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43598</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43608</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43608</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43608</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43614</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43618</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43618</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43618</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43618</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>43626</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>43626</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>43634</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>43635</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>43642</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>43643</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>43647</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>43648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>43689</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>43689</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>43689</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43699</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43700</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43700</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43700</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43700</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43705</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43713</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43714</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43717</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43718</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43725</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43725</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43725</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43746</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43748</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43748</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43754</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43761</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43767</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43773</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43774</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43788</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43790</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43790</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43793</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43798</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43801</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43812</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>43816</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43816</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43822</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43833</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43837</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43840</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43847</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43847</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43850</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43857</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43879</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43887</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43899</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43922</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43922</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43926</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43926</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43928</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43930</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43930</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>43942</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43945</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43945</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43951</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43951</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43955</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43955</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43956</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43956</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43958</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43959</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43962</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43966</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43969</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43973</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43973</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43973</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43973</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>43976</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43976</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43976</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43977</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43978</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43979</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43979</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43980</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43983</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>43983</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>43984</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>43985</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>43986</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>43991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43991</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43992</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43994</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43994</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44004</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44004</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44004</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44005</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44007</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44007</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44007</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44007</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44011</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44011</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44012</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>44012</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44013</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44013</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44013</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44018</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44028</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44034</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44034</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44048</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44050</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44054</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44055</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44055</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44061</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44064</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44082</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44082</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44092</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44092</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44095</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44102</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44104</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44109</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44112</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44113</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44116</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44120</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>44124</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44125</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44127</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>44127</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44130</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44132</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44138</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44139</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44139</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44139</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44146</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44147</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44152</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44154</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44167</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44172</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44172</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44174</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44188</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44190</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44190</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44190</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44190</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44203</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44208</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44208</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44218</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44218</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44221</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44223</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44231</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44231</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44235</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44236</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44237</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44237</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44242</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44249</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44249</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44258</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44258</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44263</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44263</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44263</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44284</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44284</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44287</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44301</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44305</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44305</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44305</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44309</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44312</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44313</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44319</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44320</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44329</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44330</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44337</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44342</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>44348</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44348</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44349</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44349</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44349</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44350</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44355</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44355</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44357</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44357</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44357</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44362</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44362</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44364</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44379</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44382</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44386</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44396</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44403</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44417</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44421</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44421</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44432</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44434</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44435</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44439</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44439</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44440</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44441</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44442</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44442</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44448</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44452</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44454</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>44455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44456</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44460</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>44460</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44461</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44461</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44462</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44462</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44466</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44467</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44473</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44473</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44475</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44484</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44484</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44489</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44490</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44490</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44490</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44491</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44497</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44501</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44501</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44502</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44502</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44502</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44503</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44503</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44509</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44509</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44512</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44512</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44516</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44522</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44525</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44525</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44525</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44530</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44532</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44540</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44540</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44540</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44540</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44544</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44544</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44544</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44544</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44544</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44544</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44545</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44546</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44547</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44547</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>44551</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44552</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44552</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44552</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44552</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44558</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44560</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44566</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44571</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44573</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44574</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44575</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44575</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44579</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44581</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44586</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44586</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44589</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44594</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44595</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44596</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44596</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44596</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44599</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44601</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44601</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44601</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>44601</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44603</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44605</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44607</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44607</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44608</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44613</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44620</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44622</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44628</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44628</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44634</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44635</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44635</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44641</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44651</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44651</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44652</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44657</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44663</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44665</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44678</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44678</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44679</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44680</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44684</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44685</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44686</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44686</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44686</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44686</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44686</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>44690</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44690</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44690</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44691</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44692</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44692</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44692</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44699</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44699</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44699</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44701</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44703</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44705</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44705</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>44704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44705</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44705</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44706</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44706</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44711</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44713</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44714</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44713</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44720</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44720</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44720</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44722</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44722</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44722</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44725</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44728</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>44729</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44728</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44729</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44729</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44728</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44729</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44729</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44732</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44734</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44739</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44742</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44743</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44748</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44757</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44763</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44763</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44764</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44765</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44765</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44768</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44775</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44775</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44775</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44777</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44781</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>44782</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44783</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44783</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44785</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44788</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>44788</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44788</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>44788</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44789</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44789</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44789</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44792</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44792</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>44797</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44797</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44797</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44797</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44798</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44799</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44804</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44806</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>44808</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44811</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44811</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44811</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44812</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44812</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44812</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44813</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44813</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44816</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44816</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44816</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44816</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44817</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44818</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44820</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>44823</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44823</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44823</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44823</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44824</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44825</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>44825</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>44825</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44826</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>44826</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44830</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44832</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44832</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44832</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44833</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44838</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44841</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>44841</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44841</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44844</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44848</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44848</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>44851</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44851</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44851</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44854</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44854</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44855</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44858</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44859</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>44862</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44866</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44866</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44868</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44868</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44869</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44872</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44872</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44872</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>44873</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44873</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44873</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44874</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44874</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44874</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44874</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44874</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44876</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>44879</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>44881</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44881</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>44881</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44886</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44886</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44886</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44886</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44887</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44888</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44888</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44888</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44888</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44888</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44893</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44893</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44894</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44894</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44895</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>44896</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44896</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44896</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44897</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44900</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44900</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44900</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>44907</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44908</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>44915</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44915</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>44915</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44915</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44916</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44916</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44929</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>44929</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44929</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44930</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44930</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44937</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44937</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44938</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>44938</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>44939</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44939</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>44939</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44942</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44943</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>44943</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44945</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44945</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>44949</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44952</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44952</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>44952</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44952</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>44952</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>44952</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>44953</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44958</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44959</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44959</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44959</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44960</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>44960</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>44960</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44960</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>44963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44964</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44964</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44964</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44965</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44965</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44967</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44968</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44968</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44970</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>44973</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44977</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44978</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>44979</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44980</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44980</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44980</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44980</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44980</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44980</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44980</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>44980</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44985</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44985</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44985</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44987</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44993</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44993</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44994</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44998</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44999</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>44999</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44999</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44999</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45001</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45016</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45019</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45019</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45019</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45020</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45020</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45020</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45020</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45027</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45029</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45029</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45034</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45041</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45041</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45042</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45043</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45044</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45044</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45044</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45044</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45045</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45055</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45056</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45058</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45061</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45062</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45062</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>45062</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45063</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45063</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45063</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45068</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>45069</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45069</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45070</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45071</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45072</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45072</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45075</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45075</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45075</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45075</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>45078</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45079</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45079</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45079</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45079</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>45086</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>45086</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45089</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45089</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45090</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45090</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45099</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45099</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45103</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45103</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>45103</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45103</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45104</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45105</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45106</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45106</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45106</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45120</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45120</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45121</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45121</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45122</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45124</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45125</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45131</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45132</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45139</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45140</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45142</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45142</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45142</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45142</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45142</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45142</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>45142</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45146</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45149</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45149</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45152</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45152</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45154</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45154</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45155</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45161</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45161</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45162</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45163</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45163</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45163</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45163</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45163</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45163</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45166</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45166</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45166</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45167</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45167</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45168</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45168</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45169</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45169</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45169</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45169</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>45169</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45169</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45170</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45170</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45170</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45170</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45173</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45173</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45174</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45174</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45174</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45174</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45175</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45175</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45175</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45175</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45175</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45176</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45176</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45176</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45176</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45177</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45182</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45182</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45183</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45183</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45184</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45183</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45187</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45187</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45188</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45188</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45188</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45188</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45188</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>45189</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45189</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45191</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45195</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45195</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45196</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45197</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>45197</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45202</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45202</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45204</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45204</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45208</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45208</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45215</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45216</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45216</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45216</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>45216</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59860,7 +59860,7 @@
         <v>45216</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45216</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45216</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45216</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45216</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45216</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45217</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45218</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45218</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60403,7 +60403,7 @@
         <v>45218</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>45219</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45219</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45219</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60636,7 +60636,7 @@
         <v>45219</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60698,7 +60698,7 @@
         <v>45219</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45222</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45222</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45222</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45223</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45223</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45223</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>45231</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>45231</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>45231</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45231</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45231</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45232</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45232</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45232</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45233</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45232</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45233</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45236</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45236</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45236</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45236</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45236</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45236</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45236</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45236</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45238</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45239</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45239</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45240</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45240</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>45243</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45245</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45246</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45246</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45246</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45246</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63011,7 +63011,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45252</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45253</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45257</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45258</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>45259</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45260</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63715,7 +63715,7 @@
         <v>45260</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45261</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45264</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45266</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45267</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45267</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45267</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45268</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         <v>45268</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45269</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45271</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45271</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45271</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45271</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45272</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45272</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45272</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45273</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45275</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45287</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45288</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45288</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45289</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45295</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45296</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>45296</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -65242,7 +65242,7 @@
         <v>45296</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45297</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>45297</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45299</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45299</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45300</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45301</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45303</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45303</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45303</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65837,7 +65837,7 @@
         <v>45306</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45306</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45306</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45309</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45309</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>45313</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45313</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45313</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45320</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45324</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>45327</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66474,7 +66474,7 @@
         <v>45331</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>45336</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45336</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>45338</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -66702,7 +66702,7 @@
         <v>45343</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -66759,7 +66759,7 @@
         <v>45343</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45345</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45345</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44884</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45091</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45106</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45317</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45478</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44673</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45544</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44055</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44263</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44490</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44767</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44876</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44112</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44138</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44130</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>44218</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44686</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44442</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44605</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44525</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>44462</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44090</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44231</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44713</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44713</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44364</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44090</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44855</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44174</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44237</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44092</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44879</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44127</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44172</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44147</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44190</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44287</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44312</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44379</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44460</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44540</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44461</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44739</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44132</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44692</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44544</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44711</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44104</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44329</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44586</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44461</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44685</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44728</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44503</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44064</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44152</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44095</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44545</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44082</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44386</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44728</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44490</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44116</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44349</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44309</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44242</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44208</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44284</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44692</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44684</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44357</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44734</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45617</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45681.39703703704</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45273</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45056.82412037037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44830.575</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44874</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44790</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45617</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45357</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45364.60462962963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45734.64541666667</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45324.48376157408</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44789</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44765.52364583333</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45526.58457175926</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45303</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44348</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45183.80868055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45183.92178240741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45541.59466435185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45667</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45670.55952546297</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45677.41510416667</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44061</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45719</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45443.41045138889</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44573.52768518519</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45419.4737962963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44886</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45044.61585648148</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44844.57421296297</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45245</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45148.66540509259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44284</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44236.36252314815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45617.46939814815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45758.32194444445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45771.5834837963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45386.41466435185</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45386.42899305555</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45664</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45566.45481481482</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44433</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45232.55104166667</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45636</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>45216.56440972222</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44900</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44869</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45763.40003472222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44945</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45726</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45183</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44781.92569444444</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45623</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45534</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>44964.58133101852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44833.38618055556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44783</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45103.67951388889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45103</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44434.33675925926</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45463.95799768518</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45489.60886574074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44938</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45174.82175925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45484.48097222222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44713</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45546</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45397</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45579</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45632</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>44952</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45622.68012731482</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45513.62717592593</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45504.36773148148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45392</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45530</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45537.64859953704</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45685.54583333333</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45176.37850694444</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45271.92625</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45295</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44938.64047453704</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44939.9237037037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44998.3634375</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>44930.69663194445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45622</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44994</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45729.63112268518</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44560.51326388889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45545.69261574074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45058</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>44964</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>44628.69327546296</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45306</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45622</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44601</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45548</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44599</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45625.36425925926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45358.34773148148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44900.4591087963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>44900</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45120.92688657407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45463.33690972222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45300</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45525.38375</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45736</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45184.54789351852</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>44664.94773148148</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45596.27561342593</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45271.42679398148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45076</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44603</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45462</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45579</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45231.63473379629</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45671.61848379629</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45170</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45687.44737268519</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44208</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45063</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45754</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45125</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45593.47171296296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45560</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45637</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44692</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45573.66002314815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45554</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45791</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45574.39741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>44208</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45509.32942129629</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45734.55638888889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45792</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45791</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45055</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45236</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45791</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45435.61346064815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45790.89</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44551</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>44943.92533564815</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45719.50333333333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45631.43291666666</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45175.67030092593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>45835.42241898148</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45173</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45170.51297453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44644.71585648148</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45372.51966435185</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45838.46716435185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45838.4712037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45169.5165625</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45642.92408564815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45835.47226851852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45253</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45701.60899305555</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>44589</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45622</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45644.45839120371</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44907</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45569</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45622</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45835.45920138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44607.46671296296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45835.44370370371</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45176</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45204</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45545</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45603.46905092592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45131.4106712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45835.45228009259</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45223</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45607.47730324074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45607.49569444444</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45448</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45590.34556712963</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45070</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44894</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45532.53859953704</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45695.48805555556</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45840.47582175926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45839</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45636.46212962963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45624.91649305556</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>44547</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45586.69104166667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45639</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44235</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45841.36012731482</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45841.37690972222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44586</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45686.44449074074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45223.495</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44236</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44690.64179398148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45219</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45622</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45271.35469907407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45799.3827662037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45799.55915509259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45841.55648148148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45582.3827662037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45799.91233796296</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45802.68767361111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44699</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>44679.44565972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45754.36946759259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45803.71337962963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45846.32989583333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44711.65472222222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44678</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45149.37282407407</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44960</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45637</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45802.66018518519</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45567.4943287037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45611.65372685185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45845.67427083333</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>44952.50115740741</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44952.55783564815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45846.39252314815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45846.46015046296</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45802.70565972223</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44953</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45216.66340277778</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45848.45990740741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45848.58239583333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45848.59746527778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>45848.6784837963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45642</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45140.50714120371</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45805.38447916666</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44728</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44704.92609953704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45020.4343287037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44231.61371527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45642</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45511</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45632.38268518518</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44763.44563657408</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45306</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45062.40555555555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44748</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>44873.42377314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45439</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44960</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45166.41370370371</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45429.92326388889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45154</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45849.5868287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44768.34793981481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45496.48064814815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45236</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45646.45193287037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45142.46318287037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45142.47361111111</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45641</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45642.33392361111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45616</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45617.44668981482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45695</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44999.49780092593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44608.68528935185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45259.65444444444</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44739.92518518519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45309.57211805556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45740.38570601852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45636.44068287037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>44720.60880787037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45810.3549537037</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45169.54965277778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44795</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45678.42084490741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45812.42760416667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>44448</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45034.44483796296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45812.39972222222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45646.44805555556</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45660</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44540.45574074074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>45189.378125</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>44823</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45762.63892361111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45855.35709490741</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45611.66996527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45624.30975694444</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45813.32945601852</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45818.50258101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45818.50530092593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44777</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45860.45087962963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44808</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45663</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45860.37251157407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45860.47178240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45320</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45859.51931712963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45859.52591435185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45817.4644212963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45818.50731481481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45818.51226851852</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45817.37618055556</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45860.41956018518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45817.29372685185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45818.49982638889</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45818.51094907407</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45544</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>44811</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>44811.56202546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45862.01456018518</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44125</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45196.54778935185</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45861.46443287037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45861.47325231481</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45824</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45636.48331018518</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>44886</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44886</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>44987</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>44349.57659722222</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45824.41685185185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45824.61436342593</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45462</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45625</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>44967.38015046297</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45826.3631712963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45357</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45826.5583449074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44985.29388888889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45825.59167824074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45827.65844907407</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45827.58907407407</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45489</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45827.64987268519</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45297.71927083333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45827.47054398148</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45350</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45019</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45345</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45243.63503472223</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45610.64039351852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45832.33273148148</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>44868.66506944445</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45832.53875</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45832.69053240741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45429.92331018519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45834.60199074074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>44054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45641</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>44900</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44965.48253472222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>44357</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>45489</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>44824.65527777778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>44806</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>44652</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45187.66037037037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44915</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>44350.61917824074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45187.344375</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45539</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44349</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45607.76726851852</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>44690</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45382.54315972222</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45546.64888888889</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45546.65302083334</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45558.30701388889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45770.53225694445</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45770.53775462963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45252</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45509.33159722222</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45001</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45539</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45434.36261574074</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45622</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45497.57481481481</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>44993.35480324074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45163</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44884</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44643</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45091</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45106</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45317</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45478</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44673</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45544</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44055</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44263</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44490</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44767</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44876</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44112</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44138</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44130</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>44218</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44686</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44442</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44605</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44525</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>44462</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44090</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44231</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44713</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44713</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44364</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44090</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44855</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44174</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44237</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44092</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44879</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44127</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44172</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44147</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44190</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44287</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44312</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44379</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44460</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44540</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44461</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44739</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44132</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44692</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44544</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44711</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44104</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44329</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44586</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44461</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44685</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44728</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44503</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44064</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44152</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44095</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44545</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44082</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44386</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44728</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44490</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44116</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44349</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44309</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44242</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44208</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44284</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44692</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44684</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44357</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44734</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45617</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45681.39703703704</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45273</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45056.82412037037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44830.575</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44874</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44790</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45617</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45357</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45364.60462962963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45734.64541666667</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45324.48376157408</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44789</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44765.52364583333</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45526.58457175926</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45303</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44348</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45183.80868055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45183.92178240741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45541.59466435185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45667</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45670.55952546297</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45677.41510416667</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44061</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45719</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45443.41045138889</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44573.52768518519</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45419.4737962963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44886</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45044.61585648148</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44844.57421296297</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45245</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45148.66540509259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44284</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44236.36252314815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45617.46939814815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45758.32194444445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45771.5834837963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45386.41466435185</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45386.42899305555</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45664</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45566.45481481482</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44433</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45232.55104166667</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45636</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>45216.56440972222</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44900</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44869</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45763.40003472222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44945</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45726</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45183</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44781.92569444444</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45623</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45534</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45574</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>44964.58133101852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44833.38618055556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44783</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45103.67951388889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45103</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44434.33675925926</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45463.95799768518</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45489.60886574074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44938</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45174.82175925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45484.48097222222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44713</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45546</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45397</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45579</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45632</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>44952</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45622.68012731482</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45513.62717592593</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45504.36773148148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45392</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45530</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45537.64859953704</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45685.54583333333</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45176.37850694444</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45271.92625</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45295</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44938.64047453704</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44939.9237037037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44998.3634375</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>44930.69663194445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45622</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44994</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45729.63112268518</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44560.51326388889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45545.69261574074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45058</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>44964</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>44628.69327546296</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45306</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45622</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44601</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45548</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44599</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45625.36425925926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45358.34773148148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44900.4591087963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>44900</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45120.92688657407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45463.33690972222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45300</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45525.38375</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45736</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45184.54789351852</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>44664.94773148148</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45596.27561342593</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45271.42679398148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45076</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44603</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45462</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45579</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45231.63473379629</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45671.61848379629</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45170</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45687.44737268519</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44208</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45063</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45754</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45125</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45593.47171296296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45560</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45637</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44692</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45573.66002314815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45554</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45791</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45574.39741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>44208</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45509.32942129629</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45734.55638888889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45792</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45791</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45055</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45236</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45791</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45435.61346064815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45790.89</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44551</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>44943.92533564815</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44596</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45719.50333333333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45631.43291666666</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45175.67030092593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>45835.42241898148</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45173</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45170.51297453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44644.71585648148</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45372.51966435185</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45838.46716435185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45838.4712037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45169.5165625</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45642.92408564815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45835.47226851852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45253</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45701.60899305555</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>44589</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45622</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45644.45839120371</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44907</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45569</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45622</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45835.45920138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44607.46671296296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45835.44370370371</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45176</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45204</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45545</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45603.46905092592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45131.4106712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45835.45228009259</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45223</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45607.47730324074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45607.49569444444</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45448</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45590.34556712963</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45070</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44894</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45532.53859953704</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45695.48805555556</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45840.47582175926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45839</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45636.46212962963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45624.91649305556</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>44547</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45586.69104166667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45639</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44235</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45841.36012731482</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45841.37690972222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44586</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45686.44449074074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45223.495</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44236</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44690.64179398148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45219</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45622</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45271.35469907407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45799.3827662037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45799.55915509259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45841.55648148148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45582.3827662037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45799.91233796296</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45802.68767361111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44699</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>44679.44565972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45754.36946759259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45803.71337962963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45846.32989583333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44711.65472222222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44678</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45149.37282407407</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44960</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45637</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45802.66018518519</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45567.4943287037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45611.65372685185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45845.67427083333</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>44952.50115740741</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44952.55783564815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45846.39252314815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45846.46015046296</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45802.70565972223</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44953</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45216.66340277778</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45848.45990740741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45848.58239583333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45848.59746527778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>45848.6784837963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45642</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45140.50714120371</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45805.38447916666</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44728</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44704.92609953704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45020.4343287037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44231.61371527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45642</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45511</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45632.38268518518</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44763.44563657408</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45306</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45062.40555555555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44748</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>44873.42377314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45439</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44960</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45166.41370370371</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45429.92326388889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45154</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45849.5868287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44768.34793981481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45496.48064814815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45236</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45646.45193287037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45142.46318287037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45142.47361111111</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45641</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45642.33392361111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45616</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45617.44668981482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45695</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44999.49780092593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44608.68528935185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45259.65444444444</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44739.92518518519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45309.57211805556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45740.38570601852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45636.44068287037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>44720.60880787037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45810.3549537037</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45169.54965277778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44795</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45678.42084490741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45812.42760416667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>44448</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45034.44483796296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45812.39972222222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45646.44805555556</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45660</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44540.45574074074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>45189.378125</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>44823</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45762.63892361111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45855.35709490741</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45611.66996527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45624.30975694444</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45813.32945601852</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45818.50258101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45818.50530092593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44777</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45860.45087962963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44808</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45663</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45860.37251157407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45860.47178240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45320</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45859.51931712963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45859.52591435185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45817.4644212963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45818.50731481481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45818.51226851852</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45817.37618055556</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45860.41956018518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45817.29372685185</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45818.49982638889</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45818.51094907407</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45544</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>44811</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>44811.56202546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45862.01456018518</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44125</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45196.54778935185</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45861.46443287037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45861.47325231481</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45824</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45636.48331018518</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>44886</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44886</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>44987</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>44349.57659722222</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45824.41685185185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45824.61436342593</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45462</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45625</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>44967.38015046297</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45826.3631712963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45357</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45826.5583449074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44985.29388888889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45825.59167824074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45827.65844907407</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45827.58907407407</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45489</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45827.64987268519</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45297.71927083333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45827.47054398148</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45350</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45019</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45345</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45243.63503472223</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45610.64039351852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45832.33273148148</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>44868.66506944445</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45832.53875</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45832.69053240741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45429.92331018519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45834.60199074074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>44054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45641</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>44900</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44965.48253472222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>44357</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>45489</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>44824.65527777778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>44806</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>44652</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45187.66037037037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44915</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>44350.61917824074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45187.344375</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45539</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>44349</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45607.76726851852</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>44690</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45382.54315972222</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45546.64888888889</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45546.65302083334</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45558.30701388889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45770.53225694445</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45770.53775462963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45252</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45509.33159722222</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45001</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45539</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45434.36261574074</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45622</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45497.57481481481</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>44993.35480324074</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45163</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44643</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45091</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>44884</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>45317</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44951</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44673</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45544</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45106</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44263</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44490</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44825</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44767</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44876</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44112</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44138</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44130</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44686</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44442</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44605</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44525</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44462</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44090</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44231</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44713</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44713</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44364</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44855</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44090</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44174</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44475</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44237</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44092</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44127</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44879</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44172</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44147</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44190</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44287</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44312</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44379</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44460</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44540</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44461</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44739</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44692</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44544</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44711</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>44728</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44064</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>44503</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44152</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44095</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44545</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44082</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44386</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44728</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44490</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>44116</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44349</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44242</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44309</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44208</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44284</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44357</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44692</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44684</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44734</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44104</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44830.575</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44329</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44586</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44461</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45364.60462962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45324.48376157408</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45397</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44789</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44765.52364583333</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45419.4737962963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44952</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44886</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45622.68012731482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44844.57421296297</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45685.54583333333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45392</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45245</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45183.80868055556</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45183.92178240741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44236.36252314815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45541.59466435185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45271.92625</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45386.41466435185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45386.42899305555</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44938.64047453704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44998.3634375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45058</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44964</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44628.69327546296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45306</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45548</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44601</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45120.92688657407</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45736</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45463.33690972222</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45525.38375</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45596.27561342593</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45566.45481481482</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45271.42679398148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45076</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44603</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44433</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45754</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45170</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45791</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45063</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45792</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45125</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45593.47171296296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45791</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45055</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45236</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45791</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45790.89</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45574.39741898148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45734.55638888889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45763.40003472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45569</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45435.61346064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44596</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45719.50333333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45532.53859953704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45631.43291666666</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44945</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45175.67030092593</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45173</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45170.51297453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44644.71585648148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45586.69104166667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45169.5165625</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45642.92408564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45701.60899305555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45622</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45644.45839120371</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45799.3827662037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45799.55915509259</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45622</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45799.91233796296</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44607.46671296296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45802.68767361111</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45803.71337962963</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45846.32989583333</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45204</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45545</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45802.66018518519</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45603.46905092592</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45131.4106712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45845.67427083333</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45846.39252314815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45846.46015046296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45802.70565972223</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44953</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45848.45990740741</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45848.58239583333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45848.59746527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45695.48805555556</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45848.6784837963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45805.38447916666</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45636.46212962963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>44833.38618055556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44547</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45463.95799768518</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45639</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45489.60886574074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45306</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44586</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44873.42377314815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45686.44449074074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44960</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45219</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45849.5868287037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45622</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44699</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44679.44565972222</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45754.36946759259</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>44678</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45149.37282407407</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45216.66340277778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45259.65444444444</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45513.62717592593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45309.57211805556</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45504.36773148148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45740.38570601852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45810.3549537037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45530</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45642</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45537.64859953704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45678.42084490741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45812.42760416667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44728</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45511</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45176.37850694444</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44763.44563657408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45295</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44748</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45812.39972222222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45646.44805555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44939.9237037037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44540.45574074074</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44930.69663194445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45154</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45622</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45813.32945601852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44994</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45729.63112268518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44768.34793981481</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44560.51326388889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45236</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45818.50258101852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45818.50530092593</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45545.69261574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45860.45087962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45259</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>45663</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45860.37251157407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45860.47178240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45859.51931712963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45859.52591435185</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45817.4644212963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45818.50731481481</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45818.51226851852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45817.37618055556</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45860.41956018518</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45622</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45817.29372685185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45818.49982638889</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45818.51094907407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44599</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44608.68528935185</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45625.36425925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45358.34773148148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44720.60880787037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45169.54965277778</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44900.4591087963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44900</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45862.01456018518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44448</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45861.46443287037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45861.47325231481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45824</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45824.41685185185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45824.61436342593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45300</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45826.3631712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45189.378125</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44823</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45826.5583449074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45184.54789351852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45216</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44664.94773148148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45762.63892361111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45611.66996527778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45624.30975694444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45825.59167824074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45827.65844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>44777</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44808</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45827.58907407407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45827.64987268519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45462</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45827.47054398148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45320</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45231.63473379629</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45671.61848379629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45687.44737268519</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44208</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45832.33273148148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>44811</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>44811.56202546296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45560</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45196.54778935185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45832.53875</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45832.69053240741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44886</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44886</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45573.66002314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45834.60199074074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44967.38015046297</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45357</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45835.44370370371</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44208</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45880.62158564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45880.52561342593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45019</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45345</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>45509.32942129629</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45243.63503472223</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45610.64039351852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45835.42241898148</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>44868.66506944445</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45835.45920138889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45835.47226851852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45835.45228009259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45880.35030092593</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45880.47621527778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45838.4712037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45840.47582175926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45881.44760416666</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45429.92331018519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45882.39199074074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45882.6513425926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44943.92533564815</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45838.46716435185</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45882.49252314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45554</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45882.48813657407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45839</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45855</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45883.36712962963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45372.51966435185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45884.3940162037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45883.55640046296</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45841.37690972222</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45253</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45841.36012731482</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44589</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45641</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44907</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45883.45166666667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44900</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45841.55648148148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44965.48253472222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45176</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45884.53892361111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45884.47407407407</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45223</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44357</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45607.47730324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45607.49569444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45448</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45590.34556712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45070</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>44894</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45489</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44824.65527777778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45624.91649305556</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44806</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44652</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45187.66037037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44235</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45223.495</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44236</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>44690.64179398148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44915</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45271.35469907407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45582.3827662037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44350.61917824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44711.65472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45072</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44960</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45637</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45567.4943287037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45187.344375</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45611.65372685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45539</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44952.50115740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>44952.55783564815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>44704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45089</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45140.50714120371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44704.92609953704</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>45020.4343287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>44231.61371527778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44349</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45642</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45632.38268518518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45062.40555555555</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45607.76726851852</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>44690</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45382.54315972222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45439</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45166.41370370371</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45429.92326388889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45546.64888888889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45546.65302083334</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45496.48064814815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>45646.45193287037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45142.46318287037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45142.47361111111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45641</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45642.33392361111</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45616</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45617.44668981482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45695</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44999.49780092593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45558.30701388889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45770.53225694445</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45770.53775462963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44739.92518518519</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45636.44068287037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44795</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45034.44483796296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45660</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45252</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45509.33159722222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45001</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45544</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45539</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45434.36261574074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44125</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45636.48331018518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45622</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44987</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44349.57659722222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45497.57481481481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45625</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44993.35480324074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45681.39703703704</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45428</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>44985.29388888889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>44874</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45617</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45357</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45489</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45297.71927083333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45526.58457175926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45350</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45303</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>44348</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45617</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45273</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45670.55952546297</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45056.82412037037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45677.41510416667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45734.64541666667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45443.41045138889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44284</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45617.46939814815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45758.32194444445</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44061</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45719</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45664</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>44573.52768518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45232.55104166667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45636</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45216.56440972222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45044.61585648148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45726</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45148.66540509259</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>44781.92569444444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45623</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45534</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45574</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45771.5834837963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45037</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45103</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>44938</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45174.82175925926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>44900</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>44869</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45484.48097222222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45183</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>44964.58133101852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>44783</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45103.67951388889</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>44434.33675925926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>44713</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45546</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45579</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45632</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44643</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45091</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>44884</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>45317</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>44951</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44673</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45544</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45106</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44263</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44490</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44825</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44767</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44876</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44112</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44138</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44130</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44686</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44442</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44605</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44525</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44462</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44090</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44231</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44713</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44713</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44364</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44855</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44090</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44174</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44475</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44237</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44092</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44127</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44879</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44172</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44147</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44190</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44287</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44312</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44379</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44460</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44540</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44461</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44739</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44692</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44544</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44711</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>44728</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44064</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>44503</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44152</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44095</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44545</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44082</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44386</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44728</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44490</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>44116</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44349</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44242</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44309</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44208</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44284</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44357</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44692</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44684</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44734</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44104</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44830.575</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44329</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44586</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44461</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45364.60462962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45324.48376157408</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45397</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44789</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44765.52364583333</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45419.4737962963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44952</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44886</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45622.68012731482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44844.57421296297</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45685.54583333333</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45392</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45245</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45183.80868055556</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45183.92178240741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44236.36252314815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45541.59466435185</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45271.92625</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45386.41466435185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45386.42899305555</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44938.64047453704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44998.3634375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45058</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44964</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44628.69327546296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45306</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45548</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44601</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45120.92688657407</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45736</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45463.33690972222</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45525.38375</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45596.27561342593</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45566.45481481482</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45271.42679398148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45076</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44603</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44433</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45754</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45170</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45791</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45063</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45792</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45125</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45593.47171296296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45791</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45055</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45236</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45791</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45790.89</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45574.39741898148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45734.55638888889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45763.40003472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45569</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45435.61346064815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44596</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45719.50333333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45532.53859953704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45631.43291666666</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44945</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45175.67030092593</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45173</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45170.51297453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44644.71585648148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45586.69104166667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45169.5165625</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45642.92408564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45701.60899305555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45622</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45644.45839120371</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45799.3827662037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45799.55915509259</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45622</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45799.91233796296</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44607.46671296296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45802.68767361111</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45803.71337962963</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45846.32989583333</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45204</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45545</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45802.66018518519</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45603.46905092592</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45131.4106712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45845.67427083333</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45846.39252314815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45846.46015046296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45802.70565972223</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44953</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45848.45990740741</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45848.58239583333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45848.59746527778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45695.48805555556</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45848.6784837963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45805.38447916666</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45636.46212962963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>44833.38618055556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44547</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45463.95799768518</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45639</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45489.60886574074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45306</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44586</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44873.42377314815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45686.44449074074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44960</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45219</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45849.5868287037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45622</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44699</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44679.44565972222</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45754.36946759259</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>44678</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45149.37282407407</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45216.66340277778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45259.65444444444</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45513.62717592593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45309.57211805556</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45504.36773148148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45740.38570601852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45810.3549537037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45530</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45642</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45537.64859953704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45678.42084490741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45812.42760416667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44728</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45511</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45176.37850694444</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44763.44563657408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45295</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44748</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45812.39972222222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45646.44805555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44939.9237037037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44540.45574074074</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44930.69663194445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45154</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45622</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45813.32945601852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44994</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45729.63112268518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44768.34793981481</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44560.51326388889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45236</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45818.50258101852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45818.50530092593</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45545.69261574074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45860.45087962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45259</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>45663</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45860.37251157407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45860.47178240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45859.51931712963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45859.52591435185</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45817.4644212963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45818.50731481481</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45818.51226851852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45817.37618055556</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45860.41956018518</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45622</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45817.29372685185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45818.49982638889</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45818.51094907407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44599</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44608.68528935185</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45625.36425925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45358.34773148148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44720.60880787037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45169.54965277778</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44900.4591087963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44900</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45862.01456018518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44448</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45861.46443287037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45861.47325231481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45824</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45824.41685185185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45824.61436342593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45300</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45826.3631712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45189.378125</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44823</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45826.5583449074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45184.54789351852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45216</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44664.94773148148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45762.63892361111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45611.66996527778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45624.30975694444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45825.59167824074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45827.65844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>44777</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44808</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45827.58907407407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45827.64987268519</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45462</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45827.47054398148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45320</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45231.63473379629</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45671.61848379629</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45687.44737268519</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44208</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45832.33273148148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>44811</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>44811.56202546296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45560</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45196.54778935185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45637</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45832.53875</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45832.69053240741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44886</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44886</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45573.66002314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45834.60199074074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44967.38015046297</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45357</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45835.44370370371</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44208</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45880.62158564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45880.52561342593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45019</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45345</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>45509.32942129629</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45243.63503472223</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45610.64039351852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45835.42241898148</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>44868.66506944445</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45835.45920138889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45835.47226851852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45835.45228009259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45880.35030092593</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45880.47621527778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45838.4712037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45840.47582175926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45881.44760416666</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45429.92331018519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45882.39199074074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45882.6513425926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44943.92533564815</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45838.46716435185</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45882.49252314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45554</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45882.48813657407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45839</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45855</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45883.36712962963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45372.51966435185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45884.3940162037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45883.55640046296</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45841.37690972222</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45253</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45841.36012731482</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44589</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45641</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44907</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45883.45166666667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44900</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45841.55648148148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44965.48253472222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45176</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45884.53892361111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45884.47407407407</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45223</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44357</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45607.47730324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45607.49569444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45448</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45590.34556712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45070</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>44894</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45489</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44824.65527777778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45624.91649305556</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44806</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44652</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45187.66037037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44235</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45223.495</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44236</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>44690.64179398148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44915</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45271.35469907407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45582.3827662037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44350.61917824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44711.65472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45072</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44960</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45637</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45567.4943287037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45187.344375</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45611.65372685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45539</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44952.50115740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>44952.55783564815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>44704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45089</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45140.50714120371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44704.92609953704</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>45020.4343287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>44231.61371527778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44349</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45642</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45632.38268518518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45062.40555555555</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45607.76726851852</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>44690</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45382.54315972222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45439</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45166.41370370371</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45429.92326388889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45546.64888888889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45546.65302083334</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45496.48064814815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>45646.45193287037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45142.46318287037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45142.47361111111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45641</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45642.33392361111</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45616</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45617.44668981482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45695</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44999.49780092593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45558.30701388889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45770.53225694445</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45770.53775462963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44739.92518518519</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45636.44068287037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44795</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45034.44483796296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45660</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45252</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45509.33159722222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45001</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45544</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45539</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45434.36261574074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>44125</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45636.48331018518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45622</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44987</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44349.57659722222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45497.57481481481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45625</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44993.35480324074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45163</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45681.39703703704</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45428</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>44985.29388888889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>44874</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45617</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45357</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45489</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45297.71927083333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45526.58457175926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45350</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45303</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>44348</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45617</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45273</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45670.55952546297</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45056.82412037037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45677.41510416667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45734.64541666667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45443.41045138889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44284</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45617.46939814815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45758.32194444445</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44061</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45719</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45664</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>44573.52768518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45232.55104166667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45636</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45216.56440972222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45044.61585648148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45726</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45148.66540509259</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>44781.92569444444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45623</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45534</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45574</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45771.5834837963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45037</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45103</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>44938</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45174.82175925926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>44900</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>44869</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45484.48097222222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45183</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>44964.58133101852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>44783</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45103.67951388889</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>44434.33675925926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>44713</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45546</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45579</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45632</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44972</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44643</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>44884</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45317</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44951</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44673</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45106</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45478</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44263</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44490</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44825</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44767</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44876</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44112</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44138</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44130</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44686</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44442</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44605</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44525</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>44462</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44090</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44231</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44713</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44713</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44855</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44090</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44475</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44237</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44174</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44092</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44127</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44879</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44172</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44147</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44190</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44287</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44312</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44379</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44460</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44540</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44461</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44739</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44692</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44711</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44544</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44104</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44329</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44586</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44461</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44685</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44728</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44503</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44152</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44082</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44095</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44545</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44386</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44728</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44116</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44349</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44490</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44309</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44692</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44208</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44684</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44284</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44734</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>44242</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44357</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44808</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45726</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44603</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44886</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45163</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44692</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45103</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44830.575</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45617</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45216</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44235</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45392</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45625</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44448</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44601</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44599</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44894</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44704</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44349</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45357</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44652</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45660</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44284</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45303</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45070</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45076</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45439</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45545</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45273</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44994</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45622</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44699</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45357</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44987</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45428</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44357</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44900</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45695</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45448</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45622</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45622</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45534</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45546</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45001</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44795</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44811</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45664</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45345</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44790</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44789</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45489</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45300</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45636</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44728</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45574</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44783</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44596</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44777</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45253</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45548</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44886</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45736</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45397</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45539</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>44806</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45622</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44208</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45306</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45790.89</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45791</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45791</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45791</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45754</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45072</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45055</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45236</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45792</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44208</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45170</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45569</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45176</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45058</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44678</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45637</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45586.69104166667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45532.53859953704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45636.48331018518</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45386.41466435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45386.42899305555</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45670.55952546297</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45622</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45622</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45799.3827662037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45799.55915509259</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45484.48097222222</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45034.44483796296</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>44690.64179398148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44690</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45625.36425925926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45802.66018518519</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45802.68767361111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45462</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45803.71337962963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45245</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45799.91233796296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45802.70565972223</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>44823</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45579</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45140.50714120371</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45560</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45174.82175925926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>44953</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45805.38447916666</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45771.5834837963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44348</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>44433</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>44560.51326388889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>44711.65472222222</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45243.63503472223</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45204</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45623</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45631.43291666666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>44873.42377314815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45740.38570601852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45196.54778935185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45306</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45419.4737962963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44930.69663194445</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44938</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45183.92178240741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45642</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>44781.92569444444</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45610.64039351852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>44960</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45236</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45189.378125</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>44907</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44998.3634375</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45810.3549537037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44960</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45148.66540509259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45364.60462962963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45539</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45758.32194444445</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45358.34773148148</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44608.68528935185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44952</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>44993.35480324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45120.92688657407</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>44811.56202546296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45056.82412037037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>45734.55638888889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45541.59466435185</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45259.65444444444</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45309.57211805556</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45131.4106712963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45812.42760416667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45582.3827662037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45646.44805555556</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45678.42084490741</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>44236.36252314815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45813.32945601852</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45812.39972222222</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45271.42679398148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45350</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>44713</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44765.52364583333</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>45545.69261574074</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45663</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45216.66340277778</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44768.34793981481</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45817.37618055556</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45817.29372685185</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45817.4644212963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45297.71927083333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45435.61346064815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45637</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45089</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45859.51931712963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45859.52591435185</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44540.45574074074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45860.45087962963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45818.50258101852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45818.50530092593</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45063</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45861.46443287037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>45231.63473379629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44349.57659722222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45860.37251157407</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45818.49982638889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45818.51094907407</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45463.95799768518</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45671.61848379629</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45149.37282407407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45677.41510416667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45860.47178240741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45175.67030092593</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45861.47325231481</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45860.41956018518</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45818.50731481481</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>45818.51226851852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45862.01456018518</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44900.4591087963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>44900</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45686.44449074074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44704.92609953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45607.47730324074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45607.49569444444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45616</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45590.34556712963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45824.61436342593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45646.45193287037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45611.65372685185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45824.41685185185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>44763.44563657408</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45509.33159722222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45154</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45824</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45537.64859953704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45504.36773148148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45219</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45825.59167824074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45184.54789351852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45695.48805555556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>44664.94773148148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45611.66996527778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45176.37850694444</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>44679.44565972222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45617</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>44628.69327546296</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45573.66002314815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45596.27561342593</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45607.76726851852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45826.5583449074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45103.67951388889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45827.65844907407</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>45827.58907407407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45827.47054398148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>45826.3631712963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45617.46939814815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45719.50333333333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45719</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>45827.64987268519</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45729.63112268518</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>45166.41370370371</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44573.52768518519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>44945</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44739.92518518519</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45497.57481481481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45574.39741898148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45173</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45832.33273148148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45223</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45644.45839120371</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45216.56440972222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44938.64047453704</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45832.69053240741</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45832.53875</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45187.66037037037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45525.38375</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45434.36261574074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45044.61585648148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45835.44370370371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45834.60199074074</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45835.45228009259</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45062.40555555555</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45701.60899305555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>44964</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>44350.61917824074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>45835.42241898148</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>44952.50115740741</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>44952.55783564815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45513.62717592593</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>44551</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45142.46318287037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>45142.47361111111</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45754.36946759259</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>45530</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45462</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45641</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45642.33392361111</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45770.53775462963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>44236</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45835.47226851852</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45509.32942129629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44868.66506944445</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45835.45920138889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>45295</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45881.44760416666</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45636.44068287037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45880.47621527778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45232.55104166667</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>44231.61371527778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45252</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45838.46716435185</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45880.52561342593</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45880.62158564815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45839</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>45603.46905092592</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45554</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45880.35030092593</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45489</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45463.33690972222</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45838.4712037037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45617.44668981482</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>44869</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45687.44737268519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45169.54965277778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>45840.47582175926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>44886</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45546.64888888889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45546.65302083334</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45882.49252314815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>44999.49780092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45882.39199074074</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45882.48813657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>44965.48253472222</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45883.36712962963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45882.6513425926</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45526.58457175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45841.55648148148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45841.36012731482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>44939.9237037037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45883.45166666667</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45639</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45020.4343287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45883.55640046296</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45125</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45855</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45320</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>45841.37690972222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>44900</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45845.67427083333</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45183.80868055556</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45271.35469907407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45642.92408564815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44915</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45632</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45169.5165625</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45884.53892361111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45187.344375</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>44874</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>44547</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45884.47407407407</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45734.64541666667</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45223.495</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44589</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>44833.38618055556</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45884.3940162037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45846.46015046296</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45170.51297453704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45593.47171296296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>44985.29388888889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45846.39252314815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45622.68012731482</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45888.32341435185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45372.51966435185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45888.42379629629</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>44607.46671296296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45019</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45846.32989583333</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45770.53225694445</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>44824.65527777778</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45848.45990740741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>44644.71585648148</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45849.5868287037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45848.58239583333</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45848.59746527778</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45890.54349537037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>44720.60880787037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>44434.33675925926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45324.48376157408</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45566.45481481482</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45848.6784837963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45382.54315972222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45489.60886574074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>44844.57421296297</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>44967.38015046297</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45544</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>44943.92533564815</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45496.48064814815</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45567.4943287037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45685.54583333333</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45636.46212962963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45624.91649305556</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45558.30701388889</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45632.38268518518</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45624.30975694444</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45763.40003472222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45641</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45642</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45271.92625</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45681.39703703704</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45762.63892361111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>44586</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>44964.58133101852</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45579</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45429.92326388889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45429.92331018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -567,7 +567,7 @@
         <v>45664</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44771</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>45296</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44840.52716435185</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>45742.63572916666</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45595.74886574074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45502.36863425926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44545</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44972</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44643</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45502.36028935185</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45534.62892361111</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>44884</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45091</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>45261.29287037037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45188.36288194444</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45317</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45297.70762731481</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45478.41214120371</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44951</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45219.46030092592</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44812.37486111111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45741.43090277778</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45791.65094907407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45673.50789351852</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45835.42466435185</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44673</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45502.42929398148</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45502.43518518518</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45106</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>45478</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44263</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44540.61243055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44490</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44825</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44711.40037037037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44767</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44774.92493055556</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>44876</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44112</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44138</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44130</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44547.40262731481</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44420.91974537037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44811.50528935185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44728.92792824074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44452.60431712963</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44357.52563657407</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44686</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44705.48375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44781.83763888889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44765.52855324074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44442</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44605</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44525</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44432.66142361111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>44462</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>44441.58484953704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44090</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44249.40599537037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44231</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44713</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44713</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44092.6435300926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44417.45212962963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44855</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44090</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44456.49701388889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44475</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44237</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44174</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44092</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44370.68188657407</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44435.61856481482</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44127</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44823.3633912037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44879</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44284</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44722.5656712963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44831.92733796296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44831.43390046297</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44816.44962962963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44172</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44147</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44190</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44287</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44312</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44812.63510416666</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44741.92570601852</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44188.50596064814</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44379</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44546.48967592593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44460</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44540</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44370.48982638889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44473.50452546297</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44502.64059027778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44473.57443287037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44651.68858796296</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44848.71773148148</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44544.51302083334</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44509.35530092593</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44461</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44739</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44132</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44692</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44691.71042824074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44797.47615740741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44439.64534722222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44711</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44412.52725694444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44544.54862268519</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44544</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44120.40053240741</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44104</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44820.49546296296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44594.62877314815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44853.97255787037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44329</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44620.64556712963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44586</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44301.67956018518</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44692.75837962963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44461</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44743.45225694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44685</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44728</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44840.95450231482</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44785.50188657407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44764.59569444445</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44711.39554398148</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44728.92789351852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44530.92103009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44711.6125462963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44503</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44566.92070601852</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44467.63489583333</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44152</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44082</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44788.54135416666</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44095</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44552.54694444445</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44545</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44386</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44728</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44116</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44502.59028935185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44127.4087037037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44634.41484953704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44218.56082175926</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44349</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44571.56971064815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44109.53175925926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44491.63751157407</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44370.49515046296</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44305.62493055555</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44382.43252314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44490</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>44732.51826388889</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44309</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44704.92618055556</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44858.39075231482</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44692</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44208</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44729.65466435185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44684</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44284</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44831.5209837963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44525.61733796296</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44734</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44728.92844907408</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>44242</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44659.47033564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44915.45592592593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45042.3791550926</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44357</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44808</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45726</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45537.43836805555</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45443.58246527778</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45706.56024305556</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45775.67856481481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45019.6284837963</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44603</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45622.48667824074</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44544.51834490741</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44886</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45163</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45296.35038194444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45618.41390046296</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45429.92321759259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44692</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45289.46237268519</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45103</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45435.50869212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44830.575</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44967.96155092592</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44967.968125</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45544.57392361111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45617</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45644.70296296296</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44848.69696759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44907.35174768518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45313.63486111111</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45573.61497685185</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45712.66641203704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45089.71152777778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45041.54736111111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45079.46560185185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45188.33112268519</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45539.38991898148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45041.5646412037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44862.41356481481</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45604.38657407407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44231.55166666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45607.68701388889</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45208.53420138889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45216</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45043.49929398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44235</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45631.60908564815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45139.35453703703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45392</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45624.65340277777</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44503.53527777778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45625</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44832.5190625</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45068.92696759259</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44448</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45222.66674768519</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44686.7058912037</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44601</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45545.70670138889</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45741.47692129629</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44599</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45238.70842592593</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44894</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44704</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44349</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45636.44318287037</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45422.53849537037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45618.36010416667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45141.92449074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45352.68155092592</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45079.43686342592</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45170.70216435185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45357</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44652</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45297.67460648148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45624.67489583333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45624.6768287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45624.6821875</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45729.53565972222</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45743.58578703704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45660</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44305.68789351852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44284</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45303</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44783.45782407407</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45742.66208333334</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45169.48854166667</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45722.50196759259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45642.65353009259</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45070</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45568.71283564815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45076</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45439.8161574074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45439</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45545.57097222222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45496.3709375</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45545</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45537.35846064815</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45273</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45748.35768518518</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44994</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45622</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44699</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45357</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45175.67440972223</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>45733.57371527778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45555.57181712963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45615.37226851852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44616.63564814815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44964.56496527778</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>45020.47074074074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45020.47482638889</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45197.33954861111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44987</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45527.34570601852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45484.39853009259</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44601.62753472223</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45258.34424768519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45303.42979166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45428</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44908.56585648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45574.67715277777</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45422.56459490741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45607.52349537037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45233.3717824074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44357</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45775.66376157408</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44900</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45695</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45506.3241087963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44595.38513888889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45448</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45622</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45622</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45177.35335648148</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45719.54538194444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45621.62126157407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45260.92565972222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>45631.43737268518</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45534</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45618.42712962963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45546</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45687.45087962963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45001</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44113.67565972222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45702.56151620371</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45741.4575</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44795</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45736.40509259259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44512.56263888889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45622.69447916667</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45246.36513888889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44859.65696759259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45250.39545138889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44830.5665162037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45769.40646990741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45771.47800925926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45545.68222222223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45628.36013888889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44502.61646990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44811</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45603.65320601852</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45664</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45603.65864583333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45345</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45345.92609953704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44895.63180555555</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45124.57927083333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44790</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44789.34496527778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44789</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45489</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45300</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45301.39141203704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45636</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45579.34450231482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44208.30796296296</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45595.54486111111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45399.64290509259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45635.71554398148</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44728</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45525.64055555555</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45537.67020833334</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45574</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45762.6605787037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44783</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45268.51303240741</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45622.47424768518</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45622.49493055556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45670.56143518518</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45695.49866898148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45631.35064814815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45287.48986111111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45455.38045138889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45734.54376157407</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>44596</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45763.60581018519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45721.48769675926</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45607.75534722222</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45533.57940972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45610.55405092592</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45610.35550925926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45777.35241898148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45691.58659722222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44777</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45457.61493055556</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45253</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45779.70166666667</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45216.60457175926</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45309.55506944445</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45548</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45149.70965277778</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45763.63564814815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45763.64425925926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45343.34635416666</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45783.56886574074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45763.60788194444</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44886</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45534.54993055556</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45336.59125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45566.55170138889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44999.47921296296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45699.34824074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45758.61561342593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45498.35340277778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45618.63685185185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45686.56731481481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45736</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45784.54953703703</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45120.92684027777</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45397</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45646.43694444445</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45784.52148148148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>44552.57103009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45162.8475925926</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45604.39825231482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45539</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45789.63913194444</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45789.52925925926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44797.45246527778</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45566.65224537037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>44806</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45532.57923611111</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45559.63951388889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45622</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45610.40315972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45681.35346064815</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45786.39515046297</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45789.54197916666</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45534.66434027778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>44525.53486111111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44208</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45601.718125</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45582.52916666667</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45306</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45499.45839120371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45499.48480324074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45140.51533564815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44788.60025462963</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45758.37297453704</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>45678.45496527778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45790.89</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45791</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45680.37916666667</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44945.41037037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45231.66075231481</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45646.45481481482</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45791</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45791.46790509259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45791</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45555.54740740741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45754</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45072</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45671.60770833334</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45222.44016203703</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45055</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45793.53853009259</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45236</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45792</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45793.5347800926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45121.92335648148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45792.43704861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45607.75846064815</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45090.7058912037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44797.36980324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45646.4496875</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45072.48825231481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45646.45672453703</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44208</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45684.66099537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45796.40721064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45191.70572916666</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45645.36635416667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45645.37596064815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45216.55601851852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45796.59533564815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45338.92774305555</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44960.62733796296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45170</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45121.60966435185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45569</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45426.43263888889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45439.55940972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45426.54793981482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45176</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45799.72726851852</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45425.5177662037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45058</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45541.67366898148</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45499.62605324074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45029.65342592593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45554.34570601852</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44678</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45562.58115740741</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45733.66342592592</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45757.55423611111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45463.95457175926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45637</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45373.38446759259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45540.44701388889</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr